--- a/order_approval_template.xlsx
+++ b/order_approval_template.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Orders" sheetId="1" r:id="rId1"/>
+    <sheet name="Dropdown Options" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -246,6 +247,52 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF1B5E20"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE8F5E9"/>
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFB71C1C"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEBEE"/>
+          <bgColor rgb="FFFFEBEE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFE65100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFF8E1"/>
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF0D47A1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE3F2FD"/>
+          <bgColor rgb="FFE3F2FD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -423,7 +470,7 @@
       </c>
       <c r="F3" t="inlineStr" s="14">
         <is>
-          <t>0740614990</t>
+          <t>254740614990</t>
         </is>
       </c>
       <c r="G3" s="14"/>
@@ -4668,7 +4715,33 @@
   <mergeCells count="1">
     <mergeCell ref="A1:S1"/>
   </mergeCells>
-  <dataValidations count="9">
+  <conditionalFormatting sqref="A3:S202">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$R3="Approved"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$R3="Rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$R3="Hold"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$R3="Under Review"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="D3:D1000">
+      <formula1>'Dropdown Options'!$A$2:$A$500</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="H3:H1000">
+      <formula1>'Dropdown Options'!$B$2:$B$500</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="J3:J1000">
+      <formula1>'Dropdown Options'!$C$2:$C$500</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="0" sqref="K3:K1000">
+      <formula1>'Dropdown Options'!$D$2:$D$500</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Choose one of: Yes, No, Pending." sqref="O3:O1000">
       <formula1>"Yes,No,Pending"</formula1>
     </dataValidation>
@@ -4697,8 +4770,100 @@
       <formula1>1/1/2020</formula1>
       <formula2>12/31/2099</formula2>
     </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Use uppercase" error="CUSTOMER NAME should be uppercase." sqref="C3:C1000">
+      <formula1>OR(C3="",EXACT(C3,UPPER(C3)))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Use uppercase" error="BRANCH should be uppercase." sqref="D3:D1000">
+      <formula1>OR(D3="",EXACT(D3,UPPER(D3)))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Use uppercase" error="COUNTY should be uppercase." sqref="H3:H1000">
+      <formula1>OR(H3="",EXACT(H3,UPPER(H3)))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Use uppercase" error="VISITED BY should be uppercase." sqref="J3:J1000">
+      <formula1>OR(J3="",EXACT(J3,UPPER(J3)))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Use uppercase" error="HB STAFF should be uppercase." sqref="K3:K1000">
+      <formula1>OR(K3="",EXACT(K3,UPPER(K3)))</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF37474F"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="4" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" t="inlineStr" s="3">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="3">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="3">
+        <is>
+          <t>Visited By</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="3">
+        <is>
+          <t>HB Staff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" t="inlineStr" s="11">
+        <is>
+          <t>MURANGA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="11">
+        <is>
+          <t>MURANGA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="11">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="11">
+        <is>
+          <t>THOMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" t="inlineStr" s="11">
+        <is>
+          <t>EMBU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="11">
+        <is>
+          <t>EMBU</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="11">
+        <is>
+          <t>KIBINGE</t>
+        </is>
+      </c>
+      <c r="D3" s="11"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D1"/>
+</worksheet>
 </file>
--- a/order_approval_template.xlsx
+++ b/order_approval_template.xlsx
@@ -448,87 +448,23 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="11"/>
-      <c r="B3" t="inlineStr" s="13">
-        <is>
-          <t>09-May-2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr" s="12">
-        <is>
-          <t>PATRICK MWANGI MAINA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="12">
-        <is>
-          <t>MURANGA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="14">
-        <is>
-          <t>113650221</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="14">
-        <is>
-          <t>254740614990</t>
-        </is>
-      </c>
+      <c r="B3" s="13"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
       <c r="G3" s="14"/>
-      <c r="H3" t="inlineStr" s="15">
-        <is>
-          <t>MURANGA</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr" s="15">
-        <is>
-          <t>GITURI NEAR KAGANDA CENTRE</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr" s="16">
-        <is>
-          <t>JOHN &amp; KIBINGE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr" s="16">
-        <is>
-          <t>THOMAS</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr" s="17">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr" s="17">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr" s="18">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr" s="18">
-        <is>
-          <t>CREATED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr" s="18">
-        <is>
-          <t>15118</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr" s="18">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr" s="19">
-        <is>
-          <t>Under Review</t>
-        </is>
-      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="18"/>
+      <c r="R3" s="19"/>
       <c r="S3" s="11"/>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -4723,7 +4659,7 @@
       <formula>$R3="Rejected"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>$R3="Hold"</formula>
+      <formula>$R3="Deferred"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="4">
       <formula>$R3="Under Review"</formula>
@@ -4745,11 +4681,11 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Choose one of: Yes, No, Pending." sqref="O3:O1000">
       <formula1>"Yes,No,Pending"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Choose one of: Pass, Fail, Pending, N/A." sqref="Q3:Q1000">
-      <formula1>"Pass,Fail,Pending,N/A"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Choose one of: Approved, Pending, Rejected." sqref="Q3:Q1000">
+      <formula1>"Approved,Pending,Rejected"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Choose one of: Approved, Rejected, Hold, Under Review." sqref="R3:R1000">
-      <formula1>"Approved,Rejected,Hold,Under Review"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Choose one of: Approved, Rejected, Deferred, Under Review." sqref="R3:R1000">
+      <formula1>"Approved,Rejected,Deferred,Under Review"</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid phone" error="Use 254XXXXXXXXX format, for example 254740614990." sqref="F3:F1000">
       <formula1>OR(F3="",AND(ISNUMBER(--F3),LEN(F3)=12,LEFT(F3,3)="254"))</formula1>
